--- a/A题_solution/stage2/result3.xlsx
+++ b/A题_solution/stage2/result3.xlsx
@@ -636,7 +636,7 @@
         <v>699.6161</v>
       </c>
       <c r="K8" t="n">
-        <v>3.004</v>
+        <v>3.003</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -671,38 +671,38 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>305.13</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>134.4</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>11100</v>
+        <v>11375.0133</v>
       </c>
       <c r="F11" t="n">
-        <v>2000</v>
+        <v>1467.0035</v>
       </c>
       <c r="G11" t="n">
         <v>1800</v>
       </c>
       <c r="H11" t="n">
-        <v>11100</v>
+        <v>12118.5434</v>
       </c>
       <c r="I11" t="n">
-        <v>2000</v>
+        <v>410.2438</v>
       </c>
       <c r="J11" t="n">
-        <v>1800</v>
+        <v>1347.0979</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3.769</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
     </row>

--- a/A题_solution/stage2/result3.xlsx
+++ b/A题_solution/stage2/result3.xlsx
@@ -556,19 +556,19 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>12636.7284</v>
+        <v>12636.7288</v>
       </c>
       <c r="F5" t="n">
-        <v>473.8965</v>
+        <v>473.8968</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12943.5783</v>
+        <v>12943.5788</v>
       </c>
       <c r="I5" t="n">
-        <v>27.5921</v>
+        <v>27.5924</v>
       </c>
       <c r="J5" t="n">
         <v>1304.6265</v>
@@ -618,16 +618,16 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>6254.2388</v>
+        <v>6254.2393</v>
       </c>
       <c r="F8" t="n">
-        <v>248.83</v>
+        <v>248.8299</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6257.2663</v>
+        <v>6257.2669</v>
       </c>
       <c r="I8" t="n">
         <v>287.5182</v>
@@ -742,19 +742,19 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>12050.3194</v>
+        <v>12050.3185</v>
       </c>
       <c r="F14" t="n">
-        <v>-730.3306</v>
+        <v>-730.3312</v>
       </c>
       <c r="G14" t="n">
         <v>1300</v>
       </c>
       <c r="H14" t="n">
-        <v>11784.2221</v>
+        <v>11784.221</v>
       </c>
       <c r="I14" t="n">
-        <v>-374.5735</v>
+        <v>-374.5744</v>
       </c>
       <c r="J14" t="n">
         <v>1250.234</v>

--- a/A题_solution/stage2/result3.xlsx
+++ b/A题_solution/stage2/result3.xlsx
@@ -439,32 +439,32 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>烟幕干扰弹投放点的x坐标 (m)</t>
+          <t>投放x</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>烟幕干扰弹投放点的y坐标 (m)</t>
+          <t>投放y</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>烟幕干扰弹投放点的z坐标 (m)</t>
+          <t>投放z</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>烟幕干扰弹起爆点的x坐标 (m)</t>
+          <t>起爆x</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>烟幕干扰弹起爆点的y坐标 (m)</t>
+          <t>起爆y</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>烟幕干扰弹起爆点的z坐标 (m)</t>
+          <t>起爆z</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -485,34 +485,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.1998</v>
+        <v>4.3558</v>
       </c>
       <c r="C2" t="n">
-        <v>82.26390000000001</v>
+        <v>89.4778</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>17924.8448</v>
+        <v>17930.7769</v>
       </c>
       <c r="F2" t="n">
-        <v>9.1676</v>
+        <v>9.9613</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>17924.8448</v>
+        <v>17930.7769</v>
       </c>
       <c r="I2" t="n">
-        <v>9.1676</v>
+        <v>9.9613</v>
       </c>
       <c r="J2" t="n">
         <v>1800</v>
       </c>
       <c r="K2" t="n">
-        <v>4.578</v>
+        <v>4.582</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -547,34 +547,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>304.5099</v>
+        <v>304.5575</v>
       </c>
       <c r="C5" t="n">
-        <v>122.7646</v>
+        <v>122.024</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>12636.7288</v>
+        <v>12633.5636</v>
       </c>
       <c r="F5" t="n">
-        <v>473.8968</v>
+        <v>480.1394</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12943.5788</v>
+        <v>12943.1098</v>
       </c>
       <c r="I5" t="n">
-        <v>27.5924</v>
+        <v>30.7143</v>
       </c>
       <c r="J5" t="n">
-        <v>1304.6265</v>
+        <v>1301.9984</v>
       </c>
       <c r="K5" t="n">
-        <v>3.928</v>
+        <v>3.945</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -671,34 +671,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>305.13</v>
+        <v>305.192</v>
       </c>
       <c r="C11" t="n">
-        <v>134.4</v>
+        <v>134.4508</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>11375.0133</v>
+        <v>11375.8771</v>
       </c>
       <c r="F11" t="n">
-        <v>1467.0035</v>
+        <v>1467.0014</v>
       </c>
       <c r="G11" t="n">
         <v>1800</v>
       </c>
       <c r="H11" t="n">
-        <v>12118.5434</v>
+        <v>12120.9121</v>
       </c>
       <c r="I11" t="n">
-        <v>410.2438</v>
+        <v>410.532</v>
       </c>
       <c r="J11" t="n">
-        <v>1347.0979</v>
+        <v>1346.9992</v>
       </c>
       <c r="K11" t="n">
-        <v>3.769</v>
+        <v>3.775</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -733,34 +733,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>126.7956</v>
+        <v>123.6855</v>
       </c>
       <c r="C14" t="n">
-        <v>139.4033</v>
+        <v>140</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>12050.3185</v>
+        <v>12128.5247</v>
       </c>
       <c r="F14" t="n">
-        <v>-730.3312</v>
+        <v>-692.5599</v>
       </c>
       <c r="G14" t="n">
         <v>1300</v>
       </c>
       <c r="H14" t="n">
-        <v>11784.221</v>
+        <v>11918.2184</v>
       </c>
       <c r="I14" t="n">
-        <v>-374.5744</v>
+        <v>-377.0455</v>
       </c>
       <c r="J14" t="n">
-        <v>1250.234</v>
+        <v>1264.0555</v>
       </c>
       <c r="K14" t="n">
-        <v>3.639</v>
+        <v>3.691</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
